--- a/artfynd/A 13391-2025 artfynd.xlsx
+++ b/artfynd/A 13391-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1032,6 +1032,126 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>123813229</v>
+      </c>
+      <c r="B5" t="n">
+        <v>57857</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Ännsiksjön, Mpd</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>632104</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6899648</v>
+      </c>
+      <c r="S5" t="n">
+        <v>25</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Njurunda</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-04-06</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>12:55</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-04-06</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>12:55</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Eva Olsson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Eva Olsson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 13391-2025 artfynd.xlsx
+++ b/artfynd/A 13391-2025 artfynd.xlsx
@@ -1038,7 +1038,7 @@
         <v>123813229</v>
       </c>
       <c r="B5" t="n">
-        <v>57857</v>
+        <v>57860</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 13391-2025 artfynd.xlsx
+++ b/artfynd/A 13391-2025 artfynd.xlsx
@@ -1038,7 +1038,7 @@
         <v>123813229</v>
       </c>
       <c r="B5" t="n">
-        <v>57860</v>
+        <v>57861</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 13391-2025 artfynd.xlsx
+++ b/artfynd/A 13391-2025 artfynd.xlsx
@@ -1158,7 +1158,7 @@
         <v>124654483</v>
       </c>
       <c r="B6" t="n">
-        <v>57355</v>
+        <v>57510</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>

--- a/artfynd/A 13391-2025 artfynd.xlsx
+++ b/artfynd/A 13391-2025 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119540542</v>
+        <v>119540541</v>
       </c>
       <c r="B2" t="n">
-        <v>90846</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -700,12 +695,12 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -719,10 +714,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>632176</v>
+        <v>632172</v>
       </c>
       <c r="R2" t="n">
-        <v>6899675</v>
+        <v>6899578</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -768,12 +763,12 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>gammal barrnaturskog på moränkulle mot myr</t>
+          <t>äldre hänglavsrik barrnaturskog</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>förrötad äldre granlåga</t>
+          <t>förrötad grövre granlåga</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -795,15 +790,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119540541</v>
+        <v>119540542</v>
       </c>
       <c r="B3" t="n">
-        <v>90846</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -820,12 +810,12 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -839,10 +829,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>632172</v>
+        <v>632176</v>
       </c>
       <c r="R3" t="n">
-        <v>6899578</v>
+        <v>6899675</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -888,12 +878,12 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>äldre hänglavsrik barrnaturskog</t>
+          <t>gammal barrnaturskog på moränkulle mot myr</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>förrötad grövre granlåga</t>
+          <t>förrötad äldre granlåga</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -918,12 +908,7 @@
         <v>119540540</v>
       </c>
       <c r="B4" t="n">
-        <v>90562</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1035,15 +1020,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123813229</v>
+        <v>124654483</v>
       </c>
       <c r="B5" t="n">
-        <v>57883</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57825</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1051,16 +1031,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103015</v>
+        <v>100096</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Fiskgjuse</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Pandion haliaetus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1073,23 +1053,29 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Ännsiksjön, Mpd</t>
+          <t>Ännsiksjön, Ännsiksjön, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>632104</v>
+        <v>632097</v>
       </c>
       <c r="R5" t="n">
-        <v>6899648</v>
+        <v>6899630</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1113,22 +1099,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-04-06</t>
+          <t>2025-05-02</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-04-06</t>
+          <t>2025-05-02</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1143,27 +1129,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Eva Olsson</t>
+          <t>Olle Finnström</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Eva Olsson</t>
+          <t>Olle Finnström</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124654483</v>
+        <v>123813229</v>
       </c>
       <c r="B6" t="n">
-        <v>57510</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1171,16 +1152,16 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100096</v>
+        <v>103015</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Fiskgjuse</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pandion haliaetus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1193,29 +1174,23 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Ännsiksjön, Ännsiksjön, Mpd</t>
+          <t>Ännsiksjön, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>632097</v>
+        <v>632104</v>
       </c>
       <c r="R6" t="n">
-        <v>6899630</v>
+        <v>6899648</v>
       </c>
       <c r="S6" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1239,22 +1214,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-05-02</t>
+          <t>2025-04-06</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-05-02</t>
+          <t>2025-04-06</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1269,12 +1244,12 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Olle Finnström</t>
+          <t>Eva Olsson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Olle Finnström</t>
+          <t>Eva Olsson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>

--- a/artfynd/A 13391-2025 artfynd.xlsx
+++ b/artfynd/A 13391-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -787,6 +792,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119540541</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -902,6 +912,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119540542</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1017,6 +1032,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119540540</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1138,6 +1158,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124654483</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1253,8 +1278,20 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123813229</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>